--- a/data/mortgage.xlsx
+++ b/data/mortgage.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -439,38 +439,9 @@
         <v>notes</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>austin-mortgage</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Austin Home Mortgage</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Fixed 30yr</v>
-      </c>
-      <c r="D2">
-        <v>360000</v>
-      </c>
-      <c r="E2">
-        <v>338500</v>
-      </c>
-      <c r="F2">
-        <v>6.25</v>
-      </c>
-      <c r="G2">
-        <v>2216</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2053-09-01</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Wells Fargo. Austin rental property. Purchased 2023.</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/mortgage.xlsx
+++ b/data/mortgage.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -439,9 +439,38 @@
         <v>notes</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>cupertino-mortgage</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Cupertino Home Mortgage</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Fixed 30yr</v>
+      </c>
+      <c r="D2">
+        <v>1800000</v>
+      </c>
+      <c r="E2">
+        <v>1790000</v>
+      </c>
+      <c r="F2">
+        <v>6.75</v>
+      </c>
+      <c r="G2">
+        <v>11674</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2055-09-01</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Wells Fargo. Primary residence. $1.2M down payment funded by META stock sales. Purchased Sep 2025.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/mortgage.xlsx
+++ b/data/mortgage.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -439,38 +439,9 @@
         <v>notes</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>cupertino-mortgage</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Cupertino Home Mortgage</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Fixed 30yr</v>
-      </c>
-      <c r="D2">
-        <v>1800000</v>
-      </c>
-      <c r="E2">
-        <v>1790000</v>
-      </c>
-      <c r="F2">
-        <v>6.75</v>
-      </c>
-      <c r="G2">
-        <v>11674</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2055-09-01</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Wells Fargo. Primary residence. $1.2M down payment funded by META stock sales. Purchased Sep 2025.</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
   </ignoredErrors>
 </worksheet>
 </file>